--- a/research/traditional_assets/database/data/ireland/ireland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.02515</v>
+        <v>0.025425</v>
       </c>
       <c r="E2">
-        <v>0.11585</v>
+        <v>0.2085</v>
       </c>
       <c r="F2">
-        <v>0.15</v>
+        <v>0.114</v>
       </c>
       <c r="G2">
-        <v>0.2684216843368674</v>
+        <v>0.2022238045681109</v>
       </c>
       <c r="H2">
-        <v>0.2684216843368674</v>
+        <v>0.2022238045681109</v>
       </c>
       <c r="I2">
-        <v>0.1629112734500379</v>
+        <v>0.2957365781609135</v>
       </c>
       <c r="J2">
-        <v>0.1236844533253027</v>
+        <v>0.2501444175894427</v>
       </c>
       <c r="K2">
-        <v>953.8</v>
+        <v>2893</v>
       </c>
       <c r="L2">
-        <v>0.07631926385277055</v>
+        <v>0.2263710983654019</v>
       </c>
       <c r="M2">
-        <v>2783</v>
+        <v>5024.2</v>
       </c>
       <c r="N2">
-        <v>0.04183848810166316</v>
+        <v>0.0803781976418641</v>
       </c>
       <c r="O2">
-        <v>2.917802474313274</v>
+        <v>1.736674732111994</v>
       </c>
       <c r="P2">
-        <v>440</v>
+        <v>496.2</v>
       </c>
       <c r="Q2">
-        <v>0.006614780727535677</v>
+        <v>0.007938310909178172</v>
       </c>
       <c r="R2">
-        <v>0.4613126441602013</v>
+        <v>0.1715174559281023</v>
       </c>
       <c r="S2">
-        <v>2343</v>
+        <v>4528</v>
       </c>
       <c r="T2">
-        <v>0.8418972332015811</v>
+        <v>0.9012380080410812</v>
       </c>
       <c r="U2">
-        <v>760.0999999999999</v>
+        <v>792.4000000000001</v>
       </c>
       <c r="V2">
-        <v>0.01142703370681788</v>
+        <v>0.01267698017822004</v>
       </c>
       <c r="W2">
-        <v>0.1755949701514024</v>
+        <v>0.7363209637333672</v>
       </c>
       <c r="X2">
-        <v>0.05538920863810162</v>
+        <v>0.08862080121416596</v>
       </c>
       <c r="Y2">
-        <v>0.1202057615133008</v>
+        <v>0.6477001625192013</v>
       </c>
       <c r="Z2">
-        <v>3.585494924809035</v>
+        <v>4.686688869971186</v>
       </c>
       <c r="AA2">
-        <v>0.2641351449758729</v>
+        <v>0.775762399739095</v>
       </c>
       <c r="AB2">
-        <v>0.05121228819423315</v>
+        <v>0.08362636207500806</v>
       </c>
       <c r="AC2">
-        <v>0.2129228567816398</v>
+        <v>0.6921360376640868</v>
       </c>
       <c r="AD2">
-        <v>8516.299999999999</v>
+        <v>10917.1</v>
       </c>
       <c r="AE2">
-        <v>1058.081800290757</v>
+        <v>832.580523806708</v>
       </c>
       <c r="AF2">
-        <v>9574.381800290757</v>
+        <v>11749.68052380671</v>
       </c>
       <c r="AG2">
-        <v>8814.281800290757</v>
+        <v>10957.28052380671</v>
       </c>
       <c r="AH2">
-        <v>0.1258262564746148</v>
+        <v>0.1582306189951456</v>
       </c>
       <c r="AI2">
-        <v>0.7752923956133039</v>
+        <v>1.021464375460264</v>
       </c>
       <c r="AJ2">
-        <v>0.117005839878976</v>
+        <v>0.1491511309398302</v>
       </c>
       <c r="AK2">
-        <v>0.7605546186709879</v>
+        <v>1.02305240224203</v>
       </c>
       <c r="AL2">
-        <v>322.06</v>
+        <v>383.66</v>
       </c>
       <c r="AM2">
-        <v>312.06</v>
+        <v>366.66</v>
       </c>
       <c r="AN2">
-        <v>3.282570151094665</v>
+        <v>2.574362723135331</v>
       </c>
       <c r="AO2">
-        <v>6.277091225237533</v>
+        <v>9.745608090496793</v>
       </c>
       <c r="AP2">
-        <v>3.397425917472539</v>
+        <v>2.583837697504353</v>
       </c>
       <c r="AQ2">
-        <v>6.478241363840286</v>
+        <v>10.19745813560247</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.03759999999999999</v>
+        <v>0.05</v>
       </c>
       <c r="E3">
-        <v>-0.0973</v>
+        <v>0.105</v>
       </c>
       <c r="F3">
-        <v>0.15</v>
+        <v>0.114</v>
       </c>
       <c r="G3">
-        <v>0.2757078986587183</v>
+        <v>0.196073698608094</v>
       </c>
       <c r="H3">
-        <v>0.2757078986587183</v>
+        <v>0.196073698608094</v>
       </c>
       <c r="I3">
-        <v>0.164628551079802</v>
+        <v>0.2948333651330484</v>
       </c>
       <c r="J3">
-        <v>0.1048423930560844</v>
+        <v>0.2415043326800423</v>
       </c>
       <c r="K3">
-        <v>916</v>
+        <v>2795</v>
       </c>
       <c r="L3">
-        <v>0.07584037092233814</v>
+        <v>0.2248773030815029</v>
       </c>
       <c r="M3">
-        <v>2783</v>
+        <v>4987</v>
       </c>
       <c r="N3">
-        <v>0.04202461074760921</v>
+        <v>0.08032561915315825</v>
       </c>
       <c r="O3">
-        <v>3.0382096069869</v>
+        <v>1.784257602862254</v>
       </c>
       <c r="P3">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="Q3">
-        <v>0.006644207232823591</v>
+        <v>0.007393113934489601</v>
       </c>
       <c r="R3">
-        <v>0.4803493449781659</v>
+        <v>0.164221824686941</v>
       </c>
       <c r="S3">
-        <v>2343</v>
+        <v>4528</v>
       </c>
       <c r="T3">
-        <v>0.8418972332015811</v>
+        <v>0.9079606978143172</v>
       </c>
       <c r="U3">
-        <v>562.3</v>
+        <v>645.7</v>
       </c>
       <c r="V3">
-        <v>0.008490994834128875</v>
+        <v>0.01040029121459681</v>
       </c>
       <c r="W3">
-        <v>0.2586109542631282</v>
+        <v>1.265278406518787</v>
       </c>
       <c r="X3">
-        <v>0.0542027822152565</v>
+        <v>0.08963445199432561</v>
       </c>
       <c r="Y3">
-        <v>0.2044081720478717</v>
+        <v>1.175643954524461</v>
       </c>
       <c r="Z3">
-        <v>3.828352618119285</v>
+        <v>5.215080589903747</v>
       </c>
       <c r="AA3">
-        <v>0.4013736499461519</v>
+        <v>1.259464557737345</v>
       </c>
       <c r="AB3">
-        <v>0.05126203094321061</v>
+        <v>0.08425238278746169</v>
       </c>
       <c r="AC3">
-        <v>0.3501116190029413</v>
+        <v>1.175212174949884</v>
       </c>
       <c r="AD3">
-        <v>8451</v>
+        <v>10860</v>
       </c>
       <c r="AE3">
-        <v>1058.081800290757</v>
+        <v>832.580523806708</v>
       </c>
       <c r="AF3">
-        <v>9509.081800290758</v>
+        <v>11692.58052380671</v>
       </c>
       <c r="AG3">
-        <v>8946.781800290759</v>
+        <v>11046.88052380671</v>
       </c>
       <c r="AH3">
-        <v>0.1255619681652199</v>
+        <v>0.1584846255151836</v>
       </c>
       <c r="AI3">
-        <v>0.8053028392855993</v>
+        <v>1.060784314394703</v>
       </c>
       <c r="AJ3">
-        <v>0.1190208310299106</v>
+        <v>0.1510546516186045</v>
       </c>
       <c r="AK3">
-        <v>0.7955677923663289</v>
+        <v>1.064566610212277</v>
       </c>
       <c r="AL3">
-        <v>319</v>
+        <v>381</v>
       </c>
       <c r="AM3">
-        <v>309</v>
+        <v>364</v>
       </c>
       <c r="AN3">
-        <v>3.335043409629045</v>
+        <v>2.642978826965198</v>
       </c>
       <c r="AO3">
-        <v>6.18808777429467</v>
+        <v>9.511811023622048</v>
       </c>
       <c r="AP3">
-        <v>3.530695264518847</v>
+        <v>2.688459606669921</v>
       </c>
       <c r="AQ3">
-        <v>6.388349514563107</v>
+        <v>9.956043956043956</v>
       </c>
     </row>
     <row r="4">
@@ -862,118 +862,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0127</v>
+        <v>0.0008500000000000001</v>
       </c>
       <c r="E4">
-        <v>0.329</v>
+        <v>0.312</v>
       </c>
       <c r="G4">
-        <v>0.05864123957091776</v>
+        <v>0.4200626959247649</v>
       </c>
       <c r="H4">
-        <v>0.05864123957091776</v>
+        <v>0.4200626959247649</v>
       </c>
       <c r="I4">
-        <v>0.1134684147794994</v>
+        <v>0.3277286976346538</v>
       </c>
       <c r="J4">
-        <v>0.1000320617007149</v>
+        <v>0.2859593538184724</v>
       </c>
       <c r="K4">
-        <v>37.8</v>
+        <v>98</v>
       </c>
       <c r="L4">
-        <v>0.0901072705601907</v>
+        <v>0.2792818466799658</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>37.2</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.08810990052108007</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.3795918367346939</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>37.2</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.08810990052108007</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.3795918367346939</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>197.8</v>
+        <v>146.7</v>
       </c>
       <c r="V4">
-        <v>0.6714188730482009</v>
+        <v>0.3474656560871625</v>
       </c>
       <c r="W4">
-        <v>0.09257898603967669</v>
+        <v>0.2073635209479475</v>
       </c>
       <c r="X4">
-        <v>0.05657563506094675</v>
+        <v>0.08760715043400633</v>
       </c>
       <c r="Y4">
-        <v>0.03600335097872994</v>
+        <v>0.1197563705139412</v>
       </c>
       <c r="Z4">
-        <v>1.26855967824851</v>
+        <v>1.02133480804494</v>
       </c>
       <c r="AA4">
-        <v>0.126896640005594</v>
+        <v>0.2920602417408446</v>
       </c>
       <c r="AB4">
-        <v>0.0511625454452557</v>
+        <v>0.08300034136255442</v>
       </c>
       <c r="AC4">
-        <v>0.07573409456033828</v>
+        <v>0.2090599003782901</v>
       </c>
       <c r="AD4">
-        <v>65.3</v>
+        <v>57.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>65.3</v>
+        <v>57.1</v>
       </c>
       <c r="AG4">
-        <v>-132.5</v>
+        <v>-89.59999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.1814392886913031</v>
+        <v>0.1191320675985813</v>
       </c>
       <c r="AI4">
-        <v>0.1206355071125069</v>
+        <v>0.1189087880049979</v>
       </c>
       <c r="AJ4">
-        <v>-0.8173966687230104</v>
+        <v>-0.269392663860493</v>
       </c>
       <c r="AK4">
-        <v>-0.3857350800582242</v>
+        <v>-0.2686656671664168</v>
       </c>
       <c r="AL4">
-        <v>3.06</v>
+        <v>2.66</v>
       </c>
       <c r="AM4">
-        <v>3.06</v>
+        <v>2.66</v>
       </c>
       <c r="AN4">
-        <v>1.081125827814569</v>
+        <v>0.4335611237661352</v>
       </c>
       <c r="AO4">
-        <v>15.55555555555556</v>
+        <v>43.23308270676691</v>
       </c>
       <c r="AP4">
-        <v>-2.193708609271523</v>
+        <v>-0.6803340926347761</v>
       </c>
       <c r="AQ4">
-        <v>15.55555555555556</v>
+        <v>43.23308270676691</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ireland/ireland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.025425</v>
+        <v>0.0245</v>
       </c>
       <c r="E2">
-        <v>0.2085</v>
+        <v>0.216</v>
       </c>
       <c r="F2">
-        <v>0.114</v>
+        <v>0.102</v>
       </c>
       <c r="G2">
-        <v>0.2022238045681109</v>
+        <v>0.2887464987547022</v>
       </c>
       <c r="H2">
-        <v>0.2022238045681109</v>
+        <v>0.2887464987547022</v>
       </c>
       <c r="I2">
-        <v>0.2957365781609135</v>
+        <v>0.2900085502353333</v>
       </c>
       <c r="J2">
-        <v>0.2501444175894427</v>
+        <v>0.2488222455784889</v>
       </c>
       <c r="K2">
-        <v>2893</v>
+        <v>2827.3</v>
       </c>
       <c r="L2">
-        <v>0.2263710983654019</v>
+        <v>0.2089513631761376</v>
       </c>
       <c r="M2">
-        <v>5024.2</v>
+        <v>3388.2</v>
       </c>
       <c r="N2">
-        <v>0.0803781976418641</v>
+        <v>0.05770409831598452</v>
       </c>
       <c r="O2">
-        <v>1.736674732111994</v>
+        <v>1.198387153821667</v>
       </c>
       <c r="P2">
-        <v>496.2</v>
+        <v>521.2</v>
       </c>
       <c r="Q2">
-        <v>0.007938310909178172</v>
+        <v>0.008876505531636603</v>
       </c>
       <c r="R2">
-        <v>0.1715174559281023</v>
+        <v>0.184345488628727</v>
       </c>
       <c r="S2">
-        <v>4528</v>
+        <v>2867</v>
       </c>
       <c r="T2">
-        <v>0.9012380080410812</v>
+        <v>0.8461720087362021</v>
       </c>
       <c r="U2">
-        <v>792.4000000000001</v>
+        <v>892.8</v>
       </c>
       <c r="V2">
-        <v>0.01267698017822004</v>
+        <v>0.01520518829363998</v>
       </c>
       <c r="W2">
-        <v>0.7363209637333672</v>
+        <v>-1.614658365261813</v>
       </c>
       <c r="X2">
-        <v>0.08862080121416596</v>
+        <v>0.07791906613781768</v>
       </c>
       <c r="Y2">
-        <v>0.6477001625192013</v>
+        <v>-1.692577431399631</v>
       </c>
       <c r="Z2">
-        <v>4.686688869971186</v>
+        <v>5.312742803808956</v>
       </c>
       <c r="AA2">
-        <v>0.775762399739095</v>
+        <v>0.8938146438572063</v>
       </c>
       <c r="AB2">
-        <v>0.08362636207500806</v>
+        <v>0.07362186750169031</v>
       </c>
       <c r="AC2">
-        <v>0.6921360376640868</v>
+        <v>0.820192776355516</v>
       </c>
       <c r="AD2">
-        <v>10917.1</v>
+        <v>11324.8</v>
       </c>
       <c r="AE2">
-        <v>832.580523806708</v>
+        <v>761.1165381036445</v>
       </c>
       <c r="AF2">
-        <v>11749.68052380671</v>
+        <v>12085.91653810364</v>
       </c>
       <c r="AG2">
-        <v>10957.28052380671</v>
+        <v>11193.11653810364</v>
       </c>
       <c r="AH2">
-        <v>0.1582306189951456</v>
+        <v>0.1706984862875905</v>
       </c>
       <c r="AI2">
-        <v>1.021464375460264</v>
+        <v>0.9986778953606544</v>
       </c>
       <c r="AJ2">
-        <v>0.1491511309398302</v>
+        <v>0.1601077084965901</v>
       </c>
       <c r="AK2">
-        <v>1.02305240224203</v>
+        <v>0.9985725904494248</v>
       </c>
       <c r="AL2">
-        <v>383.66</v>
+        <v>470</v>
       </c>
       <c r="AM2">
-        <v>366.66</v>
+        <v>446.31</v>
       </c>
       <c r="AN2">
-        <v>2.574362723135331</v>
+        <v>2.60916044604184</v>
       </c>
       <c r="AO2">
-        <v>9.745608090496793</v>
+        <v>8.300638297872341</v>
       </c>
       <c r="AP2">
-        <v>2.583837697504353</v>
+        <v>2.57882143076759</v>
       </c>
       <c r="AQ2">
-        <v>10.19745813560247</v>
+        <v>8.741233671663194</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.05</v>
+        <v>0.0378</v>
       </c>
       <c r="E3">
-        <v>0.105</v>
+        <v>0.287</v>
       </c>
       <c r="F3">
-        <v>0.114</v>
+        <v>0.102</v>
       </c>
       <c r="G3">
-        <v>0.196073698608094</v>
+        <v>0.2903053842053157</v>
       </c>
       <c r="H3">
-        <v>0.196073698608094</v>
+        <v>0.2903053842053157</v>
       </c>
       <c r="I3">
-        <v>0.2948333651330484</v>
+        <v>0.2892983544573354</v>
       </c>
       <c r="J3">
-        <v>0.2415043326800423</v>
+        <v>0.2466425554825921</v>
       </c>
       <c r="K3">
-        <v>2795</v>
+        <v>2723</v>
       </c>
       <c r="L3">
-        <v>0.2248773030815029</v>
+        <v>0.2073718680983931</v>
       </c>
       <c r="M3">
-        <v>4987</v>
+        <v>3349</v>
       </c>
       <c r="N3">
-        <v>0.08032561915315825</v>
+        <v>0.05747678789022946</v>
       </c>
       <c r="O3">
-        <v>1.784257602862254</v>
+        <v>1.229893499816379</v>
       </c>
       <c r="P3">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="Q3">
-        <v>0.007393113934489601</v>
+        <v>0.008272263888650523</v>
       </c>
       <c r="R3">
-        <v>0.164221824686941</v>
+        <v>0.1770106500183621</v>
       </c>
       <c r="S3">
-        <v>4528</v>
+        <v>2867</v>
       </c>
       <c r="T3">
-        <v>0.9079606978143172</v>
+        <v>0.8560764407285757</v>
       </c>
       <c r="U3">
-        <v>645.7</v>
+        <v>768.5</v>
       </c>
       <c r="V3">
-        <v>0.01040029121459681</v>
+        <v>0.01318928381416582</v>
       </c>
       <c r="W3">
-        <v>1.265278406518787</v>
+        <v>-3.47765006385696</v>
       </c>
       <c r="X3">
-        <v>0.08963445199432561</v>
+        <v>0.0790479463509996</v>
       </c>
       <c r="Y3">
-        <v>1.175643954524461</v>
+        <v>-3.55669801020796</v>
       </c>
       <c r="Z3">
-        <v>5.215080589903747</v>
+        <v>5.93245770687611</v>
       </c>
       <c r="AA3">
-        <v>1.259464557737345</v>
+        <v>1.463196529116322</v>
       </c>
       <c r="AB3">
-        <v>0.08425238278746169</v>
+        <v>0.07411422104561956</v>
       </c>
       <c r="AC3">
-        <v>1.175212174949884</v>
+        <v>1.389082308070703</v>
       </c>
       <c r="AD3">
-        <v>10860</v>
+        <v>11266</v>
       </c>
       <c r="AE3">
-        <v>832.580523806708</v>
+        <v>761.1165381036445</v>
       </c>
       <c r="AF3">
-        <v>11692.58052380671</v>
+        <v>12027.11653810364</v>
       </c>
       <c r="AG3">
-        <v>11046.88052380671</v>
+        <v>11258.61653810364</v>
       </c>
       <c r="AH3">
-        <v>0.1584846255151836</v>
+        <v>0.1710970580529912</v>
       </c>
       <c r="AI3">
-        <v>1.060784314394703</v>
+        <v>1.042110310418879</v>
       </c>
       <c r="AJ3">
-        <v>0.1510546516186045</v>
+        <v>0.1619347961040135</v>
       </c>
       <c r="AK3">
-        <v>1.064566610212277</v>
+        <v>1.045114387788796</v>
       </c>
       <c r="AL3">
-        <v>381</v>
+        <v>470</v>
       </c>
       <c r="AM3">
-        <v>364</v>
+        <v>448</v>
       </c>
       <c r="AN3">
-        <v>2.642978826965198</v>
+        <v>2.681104236078058</v>
       </c>
       <c r="AO3">
-        <v>9.511811023622048</v>
+        <v>8.034042553191489</v>
       </c>
       <c r="AP3">
-        <v>2.688459606669921</v>
+        <v>2.679347105688635</v>
       </c>
       <c r="AQ3">
-        <v>9.956043956043956</v>
+        <v>8.428571428571429</v>
       </c>
     </row>
     <row r="4">
@@ -862,46 +862,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0008500000000000001</v>
+        <v>0.0112</v>
       </c>
       <c r="E4">
-        <v>0.312</v>
+        <v>0.145</v>
       </c>
       <c r="G4">
-        <v>0.4200626959247649</v>
+        <v>0.2375593898474619</v>
       </c>
       <c r="H4">
-        <v>0.4200626959247649</v>
+        <v>0.2375593898474619</v>
       </c>
       <c r="I4">
-        <v>0.3277286976346538</v>
+        <v>0.3133283320830207</v>
       </c>
       <c r="J4">
-        <v>0.2859593538184724</v>
+        <v>0.2705310019557869</v>
       </c>
       <c r="K4">
-        <v>98</v>
+        <v>104.3</v>
       </c>
       <c r="L4">
-        <v>0.2792818466799658</v>
+        <v>0.2608152038009502</v>
       </c>
       <c r="M4">
-        <v>37.2</v>
+        <v>39.2</v>
       </c>
       <c r="N4">
-        <v>0.08810990052108007</v>
+        <v>0.08714984437527791</v>
       </c>
       <c r="O4">
-        <v>0.3795918367346939</v>
+        <v>0.3758389261744967</v>
       </c>
       <c r="P4">
-        <v>37.2</v>
+        <v>39.2</v>
       </c>
       <c r="Q4">
-        <v>0.08810990052108007</v>
+        <v>0.08714984437527791</v>
       </c>
       <c r="R4">
-        <v>0.3795918367346939</v>
+        <v>0.3758389261744967</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -910,73 +910,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>146.7</v>
+        <v>124.3</v>
       </c>
       <c r="V4">
-        <v>0.3474656560871625</v>
+        <v>0.276345042240996</v>
       </c>
       <c r="W4">
-        <v>0.2073635209479475</v>
+        <v>0.2483333333333333</v>
       </c>
       <c r="X4">
-        <v>0.08760715043400633</v>
+        <v>0.07679018592463575</v>
       </c>
       <c r="Y4">
-        <v>0.1197563705139412</v>
+        <v>0.1715431474086976</v>
       </c>
       <c r="Z4">
-        <v>1.02133480804494</v>
+        <v>1.199244287170875</v>
       </c>
       <c r="AA4">
-        <v>0.2920602417408446</v>
+        <v>0.3244327585980903</v>
       </c>
       <c r="AB4">
-        <v>0.08300034136255442</v>
+        <v>0.07312951395776106</v>
       </c>
       <c r="AC4">
-        <v>0.2090599003782901</v>
+        <v>0.2513032446403292</v>
       </c>
       <c r="AD4">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="AG4">
-        <v>-89.59999999999999</v>
+        <v>-65.5</v>
       </c>
       <c r="AH4">
-        <v>0.1191320675985813</v>
+        <v>0.1156114825009831</v>
       </c>
       <c r="AI4">
-        <v>0.1189087880049979</v>
+        <v>0.1048502139800285</v>
       </c>
       <c r="AJ4">
-        <v>-0.269392663860493</v>
+        <v>-0.170439760603695</v>
       </c>
       <c r="AK4">
-        <v>-0.2686656671664168</v>
+        <v>-0.150057273768614</v>
       </c>
       <c r="AL4">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>2.66</v>
+        <v>-1.69</v>
       </c>
       <c r="AN4">
-        <v>0.4335611237661352</v>
-      </c>
-      <c r="AO4">
-        <v>43.23308270676691</v>
+        <v>0.4248554913294798</v>
       </c>
       <c r="AP4">
-        <v>-0.6803340926347761</v>
+        <v>-0.4732658959537572</v>
       </c>
       <c r="AQ4">
-        <v>43.23308270676691</v>
+        <v>-74.14201183431953</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ireland/ireland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0245</v>
+        <v>0.0649</v>
       </c>
       <c r="E2">
-        <v>0.216</v>
+        <v>0.101</v>
       </c>
       <c r="F2">
-        <v>0.102</v>
+        <v>0.112</v>
       </c>
       <c r="G2">
-        <v>0.2887464987547022</v>
+        <v>0.2875519228192416</v>
       </c>
       <c r="H2">
-        <v>0.2887464987547022</v>
+        <v>0.2875519228192416</v>
       </c>
       <c r="I2">
-        <v>0.2900085502353333</v>
+        <v>0.2550794346984481</v>
       </c>
       <c r="J2">
-        <v>0.2488222455784889</v>
+        <v>0.1999726511645381</v>
       </c>
       <c r="K2">
-        <v>2827.3</v>
+        <v>2436</v>
       </c>
       <c r="L2">
-        <v>0.2089513631761376</v>
+        <v>0.1632051453838939</v>
       </c>
       <c r="M2">
-        <v>3388.2</v>
+        <v>2288</v>
       </c>
       <c r="N2">
-        <v>0.05770409831598452</v>
+        <v>0.0294563703263117</v>
       </c>
       <c r="O2">
-        <v>1.198387153821667</v>
+        <v>0.9392446633825944</v>
       </c>
       <c r="P2">
-        <v>521.2</v>
+        <v>539</v>
       </c>
       <c r="Q2">
-        <v>0.008876505531636603</v>
+        <v>0.00693924108648689</v>
       </c>
       <c r="R2">
-        <v>0.184345488628727</v>
+        <v>0.221264367816092</v>
       </c>
       <c r="S2">
-        <v>2867</v>
+        <v>1749</v>
       </c>
       <c r="T2">
-        <v>0.8461720087362021</v>
+        <v>0.7644230769230769</v>
       </c>
       <c r="U2">
-        <v>892.8</v>
+        <v>1064</v>
       </c>
       <c r="V2">
-        <v>0.01520518829363998</v>
+        <v>0.01369824214475334</v>
       </c>
       <c r="W2">
-        <v>-1.614658365261813</v>
+        <v>-4.156996587030717</v>
       </c>
       <c r="X2">
-        <v>0.07791906613781768</v>
+        <v>0.08415956415482981</v>
       </c>
       <c r="Y2">
-        <v>-1.692577431399631</v>
+        <v>-4.241156151185547</v>
       </c>
       <c r="Z2">
-        <v>5.312742803808956</v>
+        <v>6.25848615759869</v>
       </c>
       <c r="AA2">
-        <v>0.8938146438572063</v>
+        <v>1.251526069211573</v>
       </c>
       <c r="AB2">
-        <v>0.07362186750169031</v>
+        <v>0.07845656349689974</v>
       </c>
       <c r="AC2">
-        <v>0.820192776355516</v>
+        <v>1.173069505714673</v>
       </c>
       <c r="AD2">
-        <v>11324.8</v>
+        <v>17090</v>
       </c>
       <c r="AE2">
-        <v>761.1165381036445</v>
+        <v>718.4217884548195</v>
       </c>
       <c r="AF2">
-        <v>12085.91653810364</v>
+        <v>17808.42178845482</v>
       </c>
       <c r="AG2">
-        <v>11193.11653810364</v>
+        <v>16744.42178845482</v>
       </c>
       <c r="AH2">
-        <v>0.1706984862875905</v>
+        <v>0.1865095601156619</v>
       </c>
       <c r="AI2">
-        <v>0.9986778953606544</v>
+        <v>0.7310091316958541</v>
       </c>
       <c r="AJ2">
-        <v>0.1601077084965901</v>
+        <v>0.1773423660638761</v>
       </c>
       <c r="AK2">
-        <v>0.9985725904494248</v>
+        <v>0.7187242408407878</v>
       </c>
       <c r="AL2">
-        <v>470</v>
+        <v>706</v>
       </c>
       <c r="AM2">
-        <v>446.31</v>
+        <v>631</v>
       </c>
       <c r="AN2">
-        <v>2.60916044604184</v>
+        <v>3.821556350626118</v>
       </c>
       <c r="AO2">
-        <v>8.300638297872341</v>
+        <v>5.345609065155807</v>
       </c>
       <c r="AP2">
-        <v>2.57882143076759</v>
+        <v>3.744280364144638</v>
       </c>
       <c r="AQ2">
-        <v>8.741233671663194</v>
+        <v>5.980982567353407</v>
       </c>
     </row>
     <row r="3">
@@ -725,255 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0378</v>
+        <v>0.0649</v>
       </c>
       <c r="E3">
-        <v>0.287</v>
+        <v>0.101</v>
       </c>
       <c r="F3">
-        <v>0.102</v>
+        <v>0.112</v>
       </c>
       <c r="G3">
-        <v>0.2903053842053157</v>
+        <v>0.2875519228192416</v>
       </c>
       <c r="H3">
-        <v>0.2903053842053157</v>
+        <v>0.2875519228192416</v>
       </c>
       <c r="I3">
-        <v>0.2892983544573354</v>
+        <v>0.2550794346984481</v>
       </c>
       <c r="J3">
-        <v>0.2466425554825921</v>
+        <v>0.1999726511645381</v>
       </c>
       <c r="K3">
-        <v>2723</v>
+        <v>2436</v>
       </c>
       <c r="L3">
-        <v>0.2073718680983931</v>
+        <v>0.1632051453838939</v>
       </c>
       <c r="M3">
-        <v>3349</v>
+        <v>2288</v>
       </c>
       <c r="N3">
-        <v>0.05747678789022946</v>
+        <v>0.0294563703263117</v>
       </c>
       <c r="O3">
-        <v>1.229893499816379</v>
+        <v>0.9392446633825944</v>
       </c>
       <c r="P3">
-        <v>482</v>
+        <v>539</v>
       </c>
       <c r="Q3">
-        <v>0.008272263888650523</v>
+        <v>0.00693924108648689</v>
       </c>
       <c r="R3">
-        <v>0.1770106500183621</v>
+        <v>0.221264367816092</v>
       </c>
       <c r="S3">
-        <v>2867</v>
+        <v>1749</v>
       </c>
       <c r="T3">
-        <v>0.8560764407285757</v>
+        <v>0.7644230769230769</v>
       </c>
       <c r="U3">
-        <v>768.5</v>
+        <v>1064</v>
       </c>
       <c r="V3">
-        <v>0.01318928381416582</v>
+        <v>0.01369824214475334</v>
       </c>
       <c r="W3">
-        <v>-3.47765006385696</v>
+        <v>-4.156996587030717</v>
       </c>
       <c r="X3">
-        <v>0.0790479463509996</v>
+        <v>0.08415956415482981</v>
       </c>
       <c r="Y3">
-        <v>-3.55669801020796</v>
+        <v>-4.241156151185547</v>
       </c>
       <c r="Z3">
-        <v>5.93245770687611</v>
+        <v>6.25848615759869</v>
       </c>
       <c r="AA3">
-        <v>1.463196529116322</v>
+        <v>1.251526069211573</v>
       </c>
       <c r="AB3">
-        <v>0.07411422104561956</v>
+        <v>0.07845656349689974</v>
       </c>
       <c r="AC3">
-        <v>1.389082308070703</v>
+        <v>1.173069505714673</v>
       </c>
       <c r="AD3">
-        <v>11266</v>
+        <v>17090</v>
       </c>
       <c r="AE3">
-        <v>761.1165381036445</v>
+        <v>718.4217884548195</v>
       </c>
       <c r="AF3">
-        <v>12027.11653810364</v>
+        <v>17808.42178845482</v>
       </c>
       <c r="AG3">
-        <v>11258.61653810364</v>
+        <v>16744.42178845482</v>
       </c>
       <c r="AH3">
-        <v>0.1710970580529912</v>
+        <v>0.1865095601156619</v>
       </c>
       <c r="AI3">
-        <v>1.042110310418879</v>
+        <v>0.7310091316958541</v>
       </c>
       <c r="AJ3">
-        <v>0.1619347961040135</v>
+        <v>0.1773423660638761</v>
       </c>
       <c r="AK3">
-        <v>1.045114387788796</v>
+        <v>0.7187242408407878</v>
       </c>
       <c r="AL3">
-        <v>470</v>
+        <v>706</v>
       </c>
       <c r="AM3">
-        <v>448</v>
+        <v>631</v>
       </c>
       <c r="AN3">
-        <v>2.681104236078058</v>
+        <v>3.821556350626118</v>
       </c>
       <c r="AO3">
-        <v>8.034042553191489</v>
+        <v>5.345609065155807</v>
       </c>
       <c r="AP3">
-        <v>2.679347105688635</v>
+        <v>3.744280364144638</v>
       </c>
       <c r="AQ3">
-        <v>8.428571428571429</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FBD Holdings plc (ISE:EG7)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0112</v>
-      </c>
-      <c r="E4">
-        <v>0.145</v>
-      </c>
-      <c r="G4">
-        <v>0.2375593898474619</v>
-      </c>
-      <c r="H4">
-        <v>0.2375593898474619</v>
-      </c>
-      <c r="I4">
-        <v>0.3133283320830207</v>
-      </c>
-      <c r="J4">
-        <v>0.2705310019557869</v>
-      </c>
-      <c r="K4">
-        <v>104.3</v>
-      </c>
-      <c r="L4">
-        <v>0.2608152038009502</v>
-      </c>
-      <c r="M4">
-        <v>39.2</v>
-      </c>
-      <c r="N4">
-        <v>0.08714984437527791</v>
-      </c>
-      <c r="O4">
-        <v>0.3758389261744967</v>
-      </c>
-      <c r="P4">
-        <v>39.2</v>
-      </c>
-      <c r="Q4">
-        <v>0.08714984437527791</v>
-      </c>
-      <c r="R4">
-        <v>0.3758389261744967</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>124.3</v>
-      </c>
-      <c r="V4">
-        <v>0.276345042240996</v>
-      </c>
-      <c r="W4">
-        <v>0.2483333333333333</v>
-      </c>
-      <c r="X4">
-        <v>0.07679018592463575</v>
-      </c>
-      <c r="Y4">
-        <v>0.1715431474086976</v>
-      </c>
-      <c r="Z4">
-        <v>1.199244287170875</v>
-      </c>
-      <c r="AA4">
-        <v>0.3244327585980903</v>
-      </c>
-      <c r="AB4">
-        <v>0.07312951395776106</v>
-      </c>
-      <c r="AC4">
-        <v>0.2513032446403292</v>
-      </c>
-      <c r="AD4">
-        <v>58.8</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>58.8</v>
-      </c>
-      <c r="AG4">
-        <v>-65.5</v>
-      </c>
-      <c r="AH4">
-        <v>0.1156114825009831</v>
-      </c>
-      <c r="AI4">
-        <v>0.1048502139800285</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.170439760603695</v>
-      </c>
-      <c r="AK4">
-        <v>-0.150057273768614</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-1.69</v>
-      </c>
-      <c r="AN4">
-        <v>0.4248554913294798</v>
-      </c>
-      <c r="AP4">
-        <v>-0.4732658959537572</v>
-      </c>
-      <c r="AQ4">
-        <v>-74.14201183431953</v>
+        <v>5.980982567353407</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ireland/ireland_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0649</v>
+        <v>0.05485</v>
       </c>
       <c r="E2">
-        <v>0.101</v>
+        <v>0.05735</v>
       </c>
       <c r="F2">
         <v>0.112</v>
       </c>
       <c r="G2">
-        <v>0.2875519228192416</v>
+        <v>0.2881199688392625</v>
       </c>
       <c r="H2">
-        <v>0.2875519228192416</v>
+        <v>0.2881199688392625</v>
       </c>
       <c r="I2">
-        <v>0.2550794346984481</v>
+        <v>0.2553502754030794</v>
       </c>
       <c r="J2">
-        <v>0.1999726511645381</v>
+        <v>0.2107442760362836</v>
       </c>
       <c r="K2">
-        <v>2436</v>
+        <v>2504.9</v>
       </c>
       <c r="L2">
-        <v>0.1632051453838939</v>
+        <v>0.1626136068553622</v>
       </c>
       <c r="M2">
-        <v>2288</v>
+        <v>2330.79</v>
       </c>
       <c r="N2">
-        <v>0.0294563703263117</v>
+        <v>0.02982674360126074</v>
       </c>
       <c r="O2">
-        <v>0.9392446633825944</v>
+        <v>0.9304922352189707</v>
       </c>
       <c r="P2">
-        <v>539</v>
+        <v>577.5</v>
       </c>
       <c r="Q2">
-        <v>0.00693924108648689</v>
+        <v>0.007390174331333187</v>
       </c>
       <c r="R2">
-        <v>0.221264367816092</v>
+        <v>0.2305481256736796</v>
       </c>
       <c r="S2">
-        <v>1749</v>
+        <v>1753.29</v>
       </c>
       <c r="T2">
-        <v>0.7644230769230769</v>
+        <v>0.7522299306243806</v>
       </c>
       <c r="U2">
-        <v>1064</v>
+        <v>1204.7</v>
       </c>
       <c r="V2">
-        <v>0.01369824214475334</v>
+        <v>0.01541635154451444</v>
       </c>
       <c r="W2">
-        <v>-4.156996587030717</v>
+        <v>-2.009432535696593</v>
       </c>
       <c r="X2">
-        <v>0.08415956415482981</v>
+        <v>0.08263243811924995</v>
       </c>
       <c r="Y2">
-        <v>-4.241156151185547</v>
+        <v>-2.092064973815843</v>
       </c>
       <c r="Z2">
-        <v>6.25848615759869</v>
+        <v>5.459678045945994</v>
       </c>
       <c r="AA2">
-        <v>1.251526069211573</v>
+        <v>0.7509510877876082</v>
       </c>
       <c r="AB2">
-        <v>0.07845656349689974</v>
+        <v>0.07841174882449137</v>
       </c>
       <c r="AC2">
-        <v>1.173069505714673</v>
+        <v>0.6725393389631169</v>
       </c>
       <c r="AD2">
-        <v>17090</v>
+        <v>17147</v>
       </c>
       <c r="AE2">
         <v>718.4217884548195</v>
       </c>
       <c r="AF2">
-        <v>17808.42178845482</v>
+        <v>17865.42178845482</v>
       </c>
       <c r="AG2">
-        <v>16744.42178845482</v>
+        <v>16660.72178845482</v>
       </c>
       <c r="AH2">
-        <v>0.1865095601156619</v>
+        <v>0.1860792996340412</v>
       </c>
       <c r="AI2">
-        <v>0.7310091316958541</v>
+        <v>0.7169448836755226</v>
       </c>
       <c r="AJ2">
-        <v>0.1773423660638761</v>
+        <v>0.1757367012227588</v>
       </c>
       <c r="AK2">
-        <v>0.7187242408407878</v>
+        <v>0.7025654138525199</v>
       </c>
       <c r="AL2">
-        <v>706</v>
+        <v>708.74</v>
       </c>
       <c r="AM2">
-        <v>631</v>
+        <v>633.74</v>
       </c>
       <c r="AN2">
-        <v>3.821556350626118</v>
+        <v>3.719280740949613</v>
       </c>
       <c r="AO2">
-        <v>5.345609065155807</v>
+        <v>5.502864237943393</v>
       </c>
       <c r="AP2">
-        <v>3.744280364144638</v>
+        <v>3.61380426186036</v>
       </c>
       <c r="AQ2">
-        <v>5.980982567353407</v>
+        <v>6.154101050904156</v>
       </c>
     </row>
     <row r="3">
@@ -785,10 +785,10 @@
         <v>-4.156996587030717</v>
       </c>
       <c r="X3">
-        <v>0.08415956415482981</v>
+        <v>0.08414164986018471</v>
       </c>
       <c r="Y3">
-        <v>-4.241156151185547</v>
+        <v>-4.241138236890902</v>
       </c>
       <c r="Z3">
         <v>6.25848615759869</v>
@@ -797,10 +797,10 @@
         <v>1.251526069211573</v>
       </c>
       <c r="AB3">
-        <v>0.07845656349689974</v>
+        <v>0.07844199038946868</v>
       </c>
       <c r="AC3">
-        <v>1.173069505714673</v>
+        <v>1.173084078822104</v>
       </c>
       <c r="AD3">
         <v>17090</v>
@@ -843,6 +843,140 @@
       </c>
       <c r="AQ3">
         <v>5.980982567353407</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FBD Holdings plc (ISE:EG7)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.04480000000000001</v>
+      </c>
+      <c r="E4">
+        <v>0.0137</v>
+      </c>
+      <c r="G4">
+        <v>0.305857740585774</v>
+      </c>
+      <c r="H4">
+        <v>0.305857740585774</v>
+      </c>
+      <c r="I4">
+        <v>0.2638075313807531</v>
+      </c>
+      <c r="J4">
+        <v>0.2286331938633194</v>
+      </c>
+      <c r="K4">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="L4">
+        <v>0.144142259414226</v>
+      </c>
+      <c r="M4">
+        <v>42.79</v>
+      </c>
+      <c r="N4">
+        <v>0.09102318655605189</v>
+      </c>
+      <c r="O4">
+        <v>0.6210449927431059</v>
+      </c>
+      <c r="P4">
+        <v>38.5</v>
+      </c>
+      <c r="Q4">
+        <v>0.08189746862369708</v>
+      </c>
+      <c r="R4">
+        <v>0.5587808417997097</v>
+      </c>
+      <c r="S4">
+        <v>4.289999999999999</v>
+      </c>
+      <c r="T4">
+        <v>0.1002570694087403</v>
+      </c>
+      <c r="U4">
+        <v>140.7</v>
+      </c>
+      <c r="V4">
+        <v>0.2992980216975111</v>
+      </c>
+      <c r="W4">
+        <v>0.1381315156375301</v>
+      </c>
+      <c r="X4">
+        <v>0.08112322637831516</v>
+      </c>
+      <c r="Y4">
+        <v>0.0570082892592149</v>
+      </c>
+      <c r="Z4">
+        <v>1.095099544090357</v>
+      </c>
+      <c r="AA4">
+        <v>0.2503761063636433</v>
+      </c>
+      <c r="AB4">
+        <v>0.07838150725951404</v>
+      </c>
+      <c r="AC4">
+        <v>0.1719945991041293</v>
+      </c>
+      <c r="AD4">
+        <v>57</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>57</v>
+      </c>
+      <c r="AG4">
+        <v>-83.69999999999999</v>
+      </c>
+      <c r="AH4">
+        <v>0.1081388730791121</v>
+      </c>
+      <c r="AI4">
+        <v>0.1022604951560818</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.2166149068322981</v>
+      </c>
+      <c r="AK4">
+        <v>-0.2008639308855291</v>
+      </c>
+      <c r="AL4">
+        <v>2.74</v>
+      </c>
+      <c r="AM4">
+        <v>2.74</v>
+      </c>
+      <c r="AN4">
+        <v>0.4121475054229934</v>
+      </c>
+      <c r="AO4">
+        <v>46.02189781021897</v>
+      </c>
+      <c r="AP4">
+        <v>-0.6052060737527114</v>
+      </c>
+      <c r="AQ4">
+        <v>46.02189781021897</v>
       </c>
     </row>
   </sheetData>
